--- a/bid-loser-leads-2026-10-30.xlsx
+++ b/bid-loser-leads-2026-10-30.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="575">
   <si>
     <t xml:space="preserve">Losing company</t>
   </si>
@@ -105,117 +105,144 @@
     <t xml:space="preserve">989-496-0066</t>
   </si>
   <si>
+    <t xml:space="preserve">pcrannell@bierlein.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">bierlein.com</t>
   </si>
   <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 7 – Lost 2 state jobs: also Michner Plating demo 8/12 ($167,700 vs $125,000). Phil Crannell = Contract Administrator, 989-860-0591 (from a Bierlein proposal).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not contacted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open bid tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live Life Experience LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louisiana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D'Anna Produce Building Demolition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City of Shreveport, LA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELA Group Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask for owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 7 – Only 3.4% off, 3 days ago. No contact found — check LA Secretary of State.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dillard Trucking dba Dillard Environmental Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byron, CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04A7653 Hazardous Waste Disposal – Bay Area counties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caltrans (CA DOT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environmental Logistics, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">925-634-6850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melissar@dillardenv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dillardenv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 7 – Phone from directory (curbwaste). Also lost 06A3333 (10/6), 04A7575 (9/15), 01A6671 (9/10), 03A4220 (9/1). Wins some too. Email from company website.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 Service Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greensboro, NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abatement &amp; Demolition – Herman Park Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City of Goldsboro, NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Seasons Demolition, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336-613-8747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fcipoletti@a-1servicegroup.com; ilockwood@a-1servicegroup.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a-1servicegroup.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 7 – Lost 2 abatement bids: also Sumter SC 2/12 ($194,784 vs $160,078.50). Contact from SC DES list. 2nd email from company website.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GrayMar Environmental Services, LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12A2395 Hazardous Waste Disposal – Orange County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">866-472-9627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contactca@graymarenv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">graymarenv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 7 – Lost 5 Caltrans haz-waste bids this year (incl. 06A3332 9/22, 03A4190, 04A7565). California inbox from company website (also contact@graymarenv.com).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corley Construction LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Carolina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demolition of 347 Heritage Hills Dr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richland County, SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.E. Contracting, LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">803-754-7100</t>
+  </si>
+  <si>
     <t xml:space="preserve">Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 7 – Lost 2 state jobs: also Michner Plating demo 8/12 ($167,700 vs $125,000).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not contacted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open bid tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live Life Experience LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Louisiana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D'Anna Produce Building Demolition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City of Shreveport, LA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELA Group Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask for owner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 7 – Only 3.4% off, 3 days ago. No contact found — check LA Secretary of State.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dillard Trucking dba Dillard Environmental Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byron, CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04A7653 Hazardous Waste Disposal – Bay Area counties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caltrans (CA DOT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental Logistics, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">925-634-6850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dillardenv.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 7 – Phone from directory (curbwaste). Also lost 06A3333 (10/6), 04A7575 (9/15), 01A6671 (9/10), 03A4220 (9/1). Wins some too.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1 Service Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greensboro, NC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abatement &amp; Demolition – Herman Park Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City of Goldsboro, NC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Seasons Demolition, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336-613-8747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fcipoletti@a-1servicegroup.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a-1servicegroup.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 7 – Lost 2 abatement bids: also Sumter SC 2/12 ($194,784 vs $160,078.50). Contact from SC DES list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corley Construction LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Carolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demolition of 347 Heritage Hills Dr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richland County, SC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.E. Contracting, LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">803-754-7100</t>
-  </si>
-  <si>
     <t xml:space="preserve">Priority 7 – Likely related to Corley Lawn &amp; Construction — confirm on call. Also lost Sumter abatement 2/12 ($270,771).</t>
   </si>
   <si>
@@ -249,10 +276,13 @@
     <t xml:space="preserve">949-842-5554</t>
   </si>
   <si>
+    <t xml:space="preserve">info@costeraenv.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">costeraenv.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 7 – Phone from directory. Also lost 06A3332 (9/22), 05A3009 (8/25), 02A2537 (8/25). Won Orange Co. 12A2394.</t>
+    <t xml:space="preserve">Priority 7 – Phone from directory. Also lost 06A3332 (9/22), 05A3009 (8/25), 02A2537 (8/25). Won Orange Co. 12A2394. Email from company website; SF office 415-533-0112.</t>
   </si>
   <si>
     <t xml:space="preserve">EnviroApplications, Inc.</t>
@@ -294,7 +324,10 @@
     <t xml:space="preserve">602-258-8088</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 7 – Only 3.0% off. Founded 1997.</t>
+    <t xml:space="preserve">dickensquality.com (per Prospeo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 7 – Only 3.0% off. Founded 1997. No verified email. Pattern guess jdickens@dickensquality.com = UNVERIFIED GUESS.</t>
   </si>
   <si>
     <t xml:space="preserve">Dore &amp; Associates Contracting, Inc.</t>
@@ -327,16 +360,19 @@
     <t xml:space="preserve">Priority 7 – REJECTED — no bid bond (bonding pitch!). Also lost U. Iowa Melrose demo 7/29 ($298,200 vs $177,500). Email is estimating inbox.</t>
   </si>
   <si>
-    <t xml:space="preserve">GrayMar Environmental Services, LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12A2395 Hazardous Waste Disposal – Orange County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 6 – Lost 5 Caltrans haz-waste bids this year (incl. 06A3332 9/22, 03A4190, 04A7565).</t>
+    <t xml:space="preserve">United Pumping Service, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southern CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margaret Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">626-961-9326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 6 – Also lost 07A6365 biohazard (7/21) and 07A6377 (5/5); won 07A6448 in Aug. Contact from LA City BCA directory; no public email.</t>
   </si>
   <si>
     <t xml:space="preserve">Patriot Environmental Services</t>
@@ -357,10 +393,13 @@
     <t xml:space="preserve">562-436-2614</t>
   </si>
   <si>
+    <t xml:space="preserve">contact@patriotenv.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">patriotenvironmental.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 6 – Same day also lost 59A1396 lab cleaning ($227,223 vs $189,200). Owned by Heritage-Crystal Clean since 2022 — bigger parent.</t>
+    <t xml:space="preserve">Priority 6 – Same day also lost 59A1396 lab cleaning ($227,223 vs $189,200). Owned by Heritage-Crystal Clean since 2022 — bigger parent. Email from company website; toll-free 800-624-9136.</t>
   </si>
   <si>
     <t xml:space="preserve">Katch Environmental, Inc.</t>
@@ -384,10 +423,13 @@
     <t xml:space="preserve">559-292-6683</t>
   </si>
   <si>
+    <t xml:space="preserve">admin@katchenvironmental.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">katchenvironmental.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 6 – Lost 6 Caltrans bids since July. Was only 1.6% off on 05A3033 SLO demo job (8/6: $438,460 vs $431,681). Phone from Cal/OSHA asbestos registry.</t>
+    <t xml:space="preserve">Priority 6 – Lost 6 Caltrans bids since July. Was only 1.6% off on 05A3033 SLO demo job (8/6: $438,460 vs $431,681). Phone from Cal/OSHA asbestos registry. Email from company website.</t>
   </si>
   <si>
     <t xml:space="preserve">Taplin Enterprises, LLC</t>
@@ -399,15 +441,6 @@
     <t xml:space="preserve">Priority 5 – REJECTED — addendum not acknowledged (no price read). Paperwork pain = bid-prep pitch.</t>
   </si>
   <si>
-    <t xml:space="preserve">United Pumping Service, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Southern CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 5 – Also lost 07A6365 biohazard (7/21) and 07A6377 (5/5); won 07A6448 in Aug.</t>
-  </si>
-  <si>
     <t xml:space="preserve">12A2394 Hazardous Waste Disposal – Orange County</t>
   </si>
   <si>
@@ -435,6 +468,24 @@
     <t xml:space="preserve">Priority 5 – Phone from Cal/OSHA registry (CSLB 603409). Also lost 05A3033 SLO demo by 4.7% (8/6: $451,860 vs $431,681).</t>
   </si>
   <si>
+    <t xml:space="preserve">Hunter Consulting Inc. dba HCI Environmental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07A6438 Hazardous Waste Disposal – Los Angeles &amp; Ventura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">951-280-0118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customerservice@hcienv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hcienv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 5 – Also lost 07A6365 biohazard (7/21) and 03A4190 (7/14). Email from company website; toll-free 800-988-4424.</t>
+  </si>
+  <si>
     <t xml:space="preserve">NEO Corporation (Eastern Div.)</t>
   </si>
   <si>
@@ -474,7 +525,10 @@
     <t xml:space="preserve">417-863-7254</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 4 – Springfield HQ line.</t>
+    <t xml:space="preserve">gerkenenvironmental.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 4 – Springfield HQ line. Little Rock office 501-225-4191 (company site).</t>
   </si>
   <si>
     <t xml:space="preserve">Corley Lawn &amp; Construction, LLC</t>
@@ -495,18 +549,9 @@
     <t xml:space="preserve">San Francisco, CA</t>
   </si>
   <si>
-    <t xml:space="preserve">07A6438 Hazardous Waste Disposal – Los Angeles &amp; Ventura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Priority 4 – Also bid 05A3009 (8/25) and lost; won 03A4190 in July.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hunter Consulting Inc. dba HCI Environmental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 4 – Also lost 07A6365 biohazard (7/21) and 03A4190 (7/14).</t>
-  </si>
-  <si>
     <t xml:space="preserve">American Integrated Services, Inc.</t>
   </si>
   <si>
@@ -648,6 +693,18 @@
     <t xml:space="preserve">Priority 3 – Small business (SB: Y).</t>
   </si>
   <si>
+    <t xml:space="preserve">W.C. Maloney, LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209-942-1129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wcmaloney.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 3 – Demo/clearance contractor. Phone from company website.</t>
+  </si>
+  <si>
     <t xml:space="preserve">JM Environmental, Inc.</t>
   </si>
   <si>
@@ -687,7 +744,52 @@
     <t xml:space="preserve">330-538-2950</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 3 – Phone from Regional Chamber directory.</t>
+    <t xml:space="preserve">Priority 3 – Phone from Regional Chamber directory. No public email found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETT Environmental Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecticut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine #2 Fuel Tank Removal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City of Meriden, CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED Technologies LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabe Oshana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">860-388-1487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sales@ett-tech.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ett-tech.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 3 – Contact from CT DEEP list (2024) + company website.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brighter Horizons Environmental, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">978-970-0500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimating@bhenv.com; info@bhenv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bhenv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 3 – HQ is Ayer, MA. Estimating inbox from company website.</t>
   </si>
   <si>
     <t xml:space="preserve">Sagebrush Restoration, LLC</t>
@@ -750,12 +852,6 @@
     <t xml:space="preserve">Priority 2 – Find phone on company site.</t>
   </si>
   <si>
-    <t xml:space="preserve">W.C. Maloney, LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority 2 – Demo/clearance contractor.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Environmental Remediation Contractor</t>
   </si>
   <si>
@@ -771,24 +867,6 @@
     <t xml:space="preserve">True Blue Environmental Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecticut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engine #2 Fuel Tank Removal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City of Meriden, CT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RED Technologies LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETT Environmental Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brighter Horizons Environmental, Inc.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Five Star Remodeling &amp; Restoration</t>
   </si>
   <si>
@@ -804,7 +882,13 @@
     <t xml:space="preserve">805-641-9333</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 2 – Phone from Cal/OSHA registry.</t>
+    <t xml:space="preserve">info@precisionenv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precisionenv.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 2 – Phone from Cal/OSHA registry. Email from company website; 800-375-7786.</t>
   </si>
   <si>
     <t xml:space="preserve">Pitsch Companies dba Pitsch Wrecking</t>
@@ -816,7 +900,55 @@
     <t xml:space="preserve">616-363-4895</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 2 – Phone from 2025 South Bend bid form.</t>
+    <t xml:space="preserve">amy@pitschco.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pitschco.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 2 – Phone from 2025 South Bend bid form. Office email from a 2025 bid notice — verify.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homrich Wrecking, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carleton, MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">734-654-9800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">homrich.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 2 – No public email; call main line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midwest Demolition Contractors Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iowa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raze Buildings – 9, 10-11, 13-14 Melrose Place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Iowa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peterson Contractors, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402-475-1600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kcederburg@midwestdemo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">midwestdemo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 2 – Possible match: Midwest Demolition (Lincoln, NE) — confirm on call it's the same firm.</t>
   </si>
   <si>
     <t xml:space="preserve">Cactus Abatement &amp; Demolition, LLC</t>
@@ -870,6 +1002,15 @@
     <t xml:space="preserve">559-233-7156</t>
   </si>
   <si>
+    <t xml:space="preserve">info@parcenvironmental.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parcenvironmental.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority 2 – Phone from Cal/OSHA registry. Website lists 13 staff emails (e.g. jdavis@, sswiger@).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Environmental Abatement &amp; Solutions LLC (E.A.S., LLC)</t>
   </si>
   <si>
@@ -957,27 +1098,24 @@
     <t xml:space="preserve">313-892-7330</t>
   </si>
   <si>
+    <t xml:space="preserve">info@adamogroup.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">adamogroup.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Priority 1 – Phone + name from signed bid form.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homrich Wrecking, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carleton, MI</t>
+    <t xml:space="preserve">Priority 1 – Phone + name from signed bid form. Website also lists slouwers@ and tdelanoy@adamogroup.com.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezzar Demolition, LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algonquin, IL</t>
   </si>
   <si>
     <t xml:space="preserve">Priority 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Rezzar Demolition, LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algonquin, IL</t>
-  </si>
-  <si>
     <t xml:space="preserve">Smalley Construction, Inc.</t>
   </si>
   <si>
@@ -1000,21 +1138,6 @@
   </si>
   <si>
     <t xml:space="preserve">United Storm Water, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midwest Demolition Contractors Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iowa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raze Buildings – 9, 10-11, 13-14 Melrose Place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Iowa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peterson Contractors, Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">All American Concrete Inc.</t>
@@ -2201,7 +2324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -2239,35 +2362,37 @@
       <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="N2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>46322</v>
@@ -2279,44 +2404,44 @@
         <v>192500</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" s="5" t="n">
         <f aca="false">IF(OR(F3="",G3=""),"",(F3-G3)/G3)</f>
         <v>0.0335064935064935</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>46317</v>
@@ -2328,48 +2453,50 @@
         <v>1111986.8</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="5" t="n">
         <f aca="false">IF(OR(F4="",G4=""),"",(F4-G4)/G4)</f>
         <v>0.11865086887722</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="N4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>46317</v>
@@ -2381,619 +2508,635 @@
         <v>246100</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I5" s="5" t="n">
         <f aca="false">IF(OR(F5="",G5=""),"",(F5-G5)/G5)</f>
         <v>0.475010158472166</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20320</v>
+        <v>1250009</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>14997</v>
+        <v>923330.75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="I6" s="5" t="n">
         <f aca="false">IF(OR(F6="",G6=""),"",(F6-G6)/G6)</f>
-        <v>0.354937654197506</v>
+        <v>0.353804148730019</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="O6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>46308</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>24000</v>
+        <v>20320</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>14997</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I7" s="5" t="n">
         <f aca="false">IF(OR(F7="",G7=""),"",(F7-G7)/G7)</f>
-        <v>0.600320064012803</v>
+        <v>0.354937654197506</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>67</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>14997</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>366005</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>283875</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="I8" s="5" t="n">
         <f aca="false">IF(OR(F8="",G8=""),"",(F8-G8)/G8)</f>
-        <v>0.289317481285777</v>
+        <v>0.600320064012803</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2176500</v>
+        <v>366005</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2162985</v>
+        <v>283875</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I9" s="5" t="n">
         <f aca="false">IF(OR(F9="",G9=""),"",(F9-G9)/G9)</f>
-        <v>0.00624830962766732</v>
+        <v>0.289317481285777</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="O9" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46268</v>
+        <v>46296</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>493985</v>
+        <v>2176500</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>479750</v>
+        <v>2162985</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I10" s="5" t="n">
         <f aca="false">IF(OR(F10="",G10=""),"",(F10-G10)/G10)</f>
-        <v>0.0296717040125065</v>
+        <v>0.00624830962766732</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F11" s="4"/>
+        <v>46268</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>493985</v>
+      </c>
       <c r="G11" s="4" t="n">
-        <v>125000</v>
+        <v>479750</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I11" s="5" t="str">
+        <v>95</v>
+      </c>
+      <c r="I11" s="5" t="n">
         <f aca="false">IF(OR(F11="",G11=""),"",(F11-G11)/G11)</f>
-        <v/>
+        <v>0.0296717040125065</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>97</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>1250009</v>
-      </c>
+        <v>46246</v>
+      </c>
+      <c r="F12" s="4"/>
       <c r="G12" s="4" t="n">
-        <v>923330.75</v>
+        <v>125000</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="I12" s="5" t="str">
         <f aca="false">IF(OR(F12="",G12=""),"",(F12-G12)/G12)</f>
-        <v>0.353804148730019</v>
+        <v/>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="O12" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46301</v>
+        <v>46315</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>560127.5</v>
+        <v>1235711.25</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>408936</v>
+        <v>923330.75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I13" s="5" t="n">
         <f aca="false">IF(OR(F13="",G13=""),"",(F13-G13)/G13)</f>
-        <v>0.369719222567835</v>
+        <v>0.338319177607807</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="N13" s="2" t="s">
-        <v>110</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46282</v>
+        <v>46301</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>809000</v>
+        <v>560127.5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>301800</v>
+        <v>408936</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="I14" s="5" t="n">
         <f aca="false">IF(OR(F14="",G14=""),"",(F14-G14)/G14)</f>
+        <v>0.369719222567835</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>809000</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>301800</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <f aca="false">IF(OR(F15="",G15=""),"",(F15-G15)/G15)</f>
         <v>1.6805831676607</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4" t="n">
-        <v>205903.75</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="5" t="str">
-        <f aca="false">IF(OR(F15="",G15=""),"",(F15-G15)/G15)</f>
-        <v/>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="O15" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>1235711.25</v>
-      </c>
+        <v>46323</v>
+      </c>
+      <c r="F16" s="4"/>
       <c r="G16" s="4" t="n">
-        <v>923330.75</v>
+        <v>205903.75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I16" s="5" t="str">
         <f aca="false">IF(OR(F16="",G16=""),"",(F16-G16)/G16)</f>
-        <v>0.338319177607807</v>
+        <v/>
       </c>
       <c r="J16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>46302</v>
@@ -3005,44 +3148,44 @@
         <v>1197000</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="I17" s="5" t="n">
         <f aca="false">IF(OR(F17="",G17=""),"",(F17-G17)/G17)</f>
         <v>1.75989974937343</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>46261</v>
@@ -3054,303 +3197,311 @@
         <v>2299281</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I18" s="5" t="n">
         <f aca="false">IF(OR(F18="",G18=""),"",(F18-G18)/G18)</f>
         <v>0.756135939887295</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46317</v>
+        <v>46238</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>310001</v>
+        <v>5755605</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>246100</v>
+        <v>1694675</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="I19" s="5" t="n">
         <f aca="false">IF(OR(F19="",G19=""),"",(F19-G19)/G19)</f>
-        <v>0.259654611946363</v>
+        <v>2.396288373877</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="L19" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="M19" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>996836</v>
+        <v>310001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>848447</v>
+        <v>246100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="I20" s="5" t="n">
         <f aca="false">IF(OR(F20="",G20=""),"",(F20-G20)/G20)</f>
-        <v>0.174894837273277</v>
+        <v>0.259654611946363</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="O20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>17600</v>
+        <v>996836</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>14997</v>
+        <v>848447</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="I21" s="5" t="n">
         <f aca="false">IF(OR(F21="",G21=""),"",(F21-G21)/G21)</f>
-        <v>0.173568046942722</v>
+        <v>0.174894837273277</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K21" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="L21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="O21" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46238</v>
+        <v>46308</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2074704.5</v>
+        <v>17600</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1694675</v>
+        <v>14997</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="I22" s="5" t="n">
         <f aca="false">IF(OR(F22="",G22=""),"",(F22-G22)/G22)</f>
-        <v>0.224249192323012</v>
+        <v>0.173568046942722</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
+      <c r="L22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>170</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>46238</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5755605</v>
+        <v>2074704.5</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>1694675</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I23" s="5" t="n">
         <f aca="false">IF(OR(F23="",G23=""),"",(F23-G23)/G23)</f>
-        <v>2.396288373877</v>
+        <v>0.224249192323012</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>46224</v>
@@ -3362,40 +3513,40 @@
         <v>890013.65</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I24" s="5" t="n">
         <f aca="false">IF(OR(F24="",G24=""),"",(F24-G24)/G24)</f>
         <v>2.59893356691777</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>20</v>
@@ -3420,37 +3571,37 @@
         <v>0.782383759402148</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>46322</v>
@@ -3462,44 +3613,44 @@
         <v>192500</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I26" s="5" t="n">
         <f aca="false">IF(OR(F26="",G26=""),"",(F26-G26)/G26)</f>
         <v>0.227272727272727</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>46322</v>
@@ -3511,44 +3662,44 @@
         <v>192500</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I27" s="5" t="n">
         <f aca="false">IF(OR(F27="",G27=""),"",(F27-G27)/G27)</f>
         <v>0.333766233766234</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R27" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>46321</v>
@@ -3560,44 +3711,44 @@
         <v>92500</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="I28" s="5" t="n">
         <f aca="false">IF(OR(F28="",G28=""),"",(F28-G28)/G28)</f>
         <v>0.203243243243243</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R28" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>46321</v>
@@ -3609,44 +3760,44 @@
         <v>92500</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="I29" s="5" t="n">
         <f aca="false">IF(OR(F29="",G29=""),"",(F29-G29)/G29)</f>
         <v>1.92075675675676</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>46317</v>
@@ -3658,44 +3809,44 @@
         <v>246100</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I30" s="5" t="n">
         <f aca="false">IF(OR(F30="",G30=""),"",(F30-G30)/G30)</f>
         <v>0.173611946363267</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R30" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>46311</v>
@@ -3707,44 +3858,44 @@
         <v>10800</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="I31" s="5" t="n">
         <f aca="false">IF(OR(F31="",G31=""),"",(F31-G31)/G31)</f>
         <v>0.554907407407407</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>46311</v>
@@ -3756,44 +3907,44 @@
         <v>10800</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="I32" s="5" t="n">
         <f aca="false">IF(OR(F32="",G32=""),"",(F32-G32)/G32)</f>
         <v>0.805555555555556</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>46311</v>
@@ -3803,44 +3954,44 @@
         <v>10800</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="I33" s="5" t="str">
         <f aca="false">IF(OR(F33="",G33=""),"",(F33-G33)/G33)</f>
         <v/>
       </c>
       <c r="J33" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R33" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>46310</v>
@@ -3852,44 +4003,44 @@
         <v>848447</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I34" s="5" t="n">
         <f aca="false">IF(OR(F34="",G34=""),"",(F34-G34)/G34)</f>
         <v>0.176856067615302</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R34" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>46310</v>
@@ -3901,44 +4052,44 @@
         <v>848447</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I35" s="5" t="n">
         <f aca="false">IF(OR(F35="",G35=""),"",(F35-G35)/G35)</f>
         <v>0.17702814671983</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>46309</v>
@@ -3950,44 +4101,44 @@
         <v>40700</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="I36" s="5" t="n">
         <f aca="false">IF(OR(F36="",G36=""),"",(F36-G36)/G36)</f>
         <v>0.117936117936118</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>46309</v>
@@ -3999,44 +4150,44 @@
         <v>40700</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="I37" s="5" t="n">
         <f aca="false">IF(OR(F37="",G37=""),"",(F37-G37)/G37)</f>
         <v>0.285012285012285</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>46309</v>
@@ -4048,44 +4199,44 @@
         <v>40700</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="I38" s="5" t="n">
         <f aca="false">IF(OR(F38="",G38=""),"",(F38-G38)/G38)</f>
         <v>0.388206388206388</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R38" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>46302</v>
@@ -4097,44 +4248,44 @@
         <v>49000</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="I39" s="5" t="n">
         <f aca="false">IF(OR(F39="",G39=""),"",(F39-G39)/G39)</f>
         <v>1.02551020408163</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R39" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>46301</v>
@@ -4146,787 +4297,803 @@
         <v>189200</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I40" s="5" t="n">
         <f aca="false">IF(OR(F40="",G40=""),"",(F40-G40)/G40)</f>
         <v>0.596374207188161</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>852319</v>
+        <v>549956</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>301800</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I41" s="5" t="n">
         <f aca="false">IF(OR(F41="",G41=""),"",(F41-G41)/G41)</f>
-        <v>1.82411862160371</v>
+        <v>0.822253147779987</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
+      <c r="N41" s="2" t="s">
+        <v>224</v>
+      </c>
       <c r="O41" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5237738</v>
+        <v>852319</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>301800</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I42" s="5" t="n">
         <f aca="false">IF(OR(F42="",G42=""),"",(F42-G42)/G42)</f>
-        <v>16.3549966865474</v>
+        <v>1.82411862160371</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R42" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>215</v>
+        <v>126</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>217</v>
+        <v>43</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>155108.5</v>
+        <v>5237738</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>78552</v>
+        <v>301800</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="I43" s="5" t="n">
         <f aca="false">IF(OR(F43="",G43=""),"",(F43-G43)/G43)</f>
-        <v>0.974596445666565</v>
+        <v>16.3549966865474</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R43" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46268</v>
+        <v>46281</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>696410</v>
+        <v>155108.5</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>479750</v>
+        <v>78552</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="I44" s="5" t="n">
         <f aca="false">IF(OR(F44="",G44=""),"",(F44-G44)/G44)</f>
-        <v>0.451610213652944</v>
+        <v>0.974596445666565</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>224</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K44" s="2"/>
       <c r="L44" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>92</v>
+        <v>242</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F45" s="4"/>
+        <v>46274</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>34498</v>
+      </c>
       <c r="G45" s="4" t="n">
-        <v>125000</v>
+        <v>17600</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I45" s="5" t="str">
+        <v>244</v>
+      </c>
+      <c r="I45" s="5" t="n">
         <f aca="false">IF(OR(F45="",G45=""),"",(F45-G45)/G45)</f>
-        <v/>
+        <v>0.960113636363636</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>36</v>
+        <v>245</v>
       </c>
       <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
+      <c r="L45" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="O45" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R45" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>32</v>
+        <v>241</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46156</v>
+        <v>46274</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>258520</v>
+        <v>51000</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>196400</v>
+        <v>17600</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="I46" s="5" t="n">
         <f aca="false">IF(OR(F46="",G46=""),"",(F46-G46)/G46)</f>
-        <v>0.316293279022403</v>
+        <v>1.89772727272727</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
+      <c r="L46" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>253</v>
+      </c>
       <c r="O46" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R46" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>32</v>
+        <v>256</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>231</v>
+        <v>93</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>232</v>
+        <v>94</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>46156</v>
+        <v>46268</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>492662</v>
+        <v>696410</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>196400</v>
+        <v>479750</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>233</v>
+        <v>95</v>
       </c>
       <c r="I47" s="5" t="n">
         <f aca="false">IF(OR(F47="",G47=""),"",(F47-G47)/G47)</f>
-        <v>1.50846232179226</v>
+        <v>0.451610213652944</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>259</v>
+      </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R47" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>231</v>
+        <v>103</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46156</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>763000</v>
-      </c>
+        <v>46246</v>
+      </c>
+      <c r="F48" s="4"/>
       <c r="G48" s="4" t="n">
-        <v>196400</v>
+        <v>125000</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I48" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="I48" s="5" t="str">
         <f aca="false">IF(OR(F48="",G48=""),"",(F48-G48)/G48)</f>
-        <v>2.88492871690428</v>
+        <v/>
       </c>
       <c r="J48" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R48" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>41</v>
+        <v>265</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>42</v>
+        <v>266</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>46317</v>
+        <v>46156</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1355267.5</v>
+        <v>258520</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>1111986.8</v>
+        <v>196400</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>43</v>
+        <v>267</v>
       </c>
       <c r="I49" s="5" t="n">
         <f aca="false">IF(OR(F49="",G49=""),"",(F49-G49)/G49)</f>
-        <v>0.218780204944879</v>
+        <v>0.316293279022403</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R49" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>114</v>
+        <v>265</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>42</v>
+        <v>266</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>46282</v>
+        <v>46156</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>549956</v>
+        <v>492662</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>301800</v>
+        <v>196400</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>115</v>
+        <v>267</v>
       </c>
       <c r="I50" s="5" t="n">
         <f aca="false">IF(OR(F50="",G50=""),"",(F50-G50)/G50)</f>
-        <v>0.822253147779987</v>
+        <v>1.50846232179226</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R50" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>217</v>
+        <v>266</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>46281</v>
+        <v>46156</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>86575</v>
+        <v>763000</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>78552</v>
+        <v>196400</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="I51" s="5" t="n">
         <f aca="false">IF(OR(F51="",G51=""),"",(F51-G51)/G51)</f>
-        <v>0.102136164578878</v>
+        <v>2.88492871690428</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R51" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>244</v>
+        <v>59</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>216</v>
+        <v>42</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>217</v>
+        <v>43</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>46281</v>
+        <v>46317</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>188139.4</v>
+        <v>1355267.5</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>78552</v>
+        <v>1111986.8</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>218</v>
+        <v>44</v>
       </c>
       <c r="I52" s="5" t="n">
         <f aca="false">IF(OR(F52="",G52=""),"",(F52-G52)/G52)</f>
-        <v>1.39509369589571</v>
+        <v>0.218780204944879</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R52" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>23069</v>
+        <v>86575</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>17600</v>
+        <v>78552</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="I53" s="5" t="n">
         <f aca="false">IF(OR(F53="",G53=""),"",(F53-G53)/G53)</f>
-        <v>0.310738636363636</v>
+        <v>0.102136164578878</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R53" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>34498</v>
+        <v>188139.4</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>17600</v>
+        <v>78552</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="I54" s="5" t="n">
         <f aca="false">IF(OR(F54="",G54=""),"",(F54-G54)/G54)</f>
-        <v>0.960113636363636</v>
+        <v>1.39509369589571</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R54" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>46274</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>51000</v>
+        <v>23069</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>17600</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="I55" s="5" t="n">
         <f aca="false">IF(OR(F55="",G55=""),"",(F55-G55)/G55)</f>
-        <v>1.89772727272727</v>
+        <v>0.310738636363636</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R55" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>46268</v>
@@ -4938,44 +5105,44 @@
         <v>479750</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I56" s="5" t="n">
         <f aca="false">IF(OR(F56="",G56=""),"",(F56-G56)/G56)</f>
         <v>0.409788744137572</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>46261</v>
@@ -4987,43 +5154,47 @@
         <v>2299281</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I57" s="5" t="n">
         <f aca="false">IF(OR(F57="",G57=""),"",(F57-G57)/G57)</f>
         <v>2.93722426706436</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="O57" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R57" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>21</v>
@@ -5038,512 +5209,524 @@
         <v>125000</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I58" s="5" t="n">
         <f aca="false">IF(OR(F58="",G58=""),"",(F58-G58)/G58)</f>
         <v>0.548</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>292</v>
+      </c>
       <c r="O58" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R58" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>266</v>
+        <v>103</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46216</v>
+        <v>46246</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>648900</v>
+        <v>267400</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>569379</v>
+        <v>125000</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="I59" s="5" t="n">
         <f aca="false">IF(OR(F59="",G59=""),"",(F59-G59)/G59)</f>
-        <v>0.139662685135911</v>
+        <v>1.1392</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>270</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K59" s="2"/>
       <c r="L59" s="2" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
+      <c r="N59" s="2" t="s">
+        <v>297</v>
+      </c>
       <c r="O59" s="2" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R59" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>21</v>
+        <v>302</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46204</v>
+        <v>46232</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1516971</v>
+        <v>247000</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>886828.54</v>
+        <v>177500</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="I60" s="5" t="n">
         <f aca="false">IF(OR(F60="",G60=""),"",(F60-G60)/G60)</f>
-        <v>0.710557262850381</v>
+        <v>0.391549295774648</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>306</v>
+      </c>
       <c r="O60" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R60" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>113</v>
+        <v>309</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>42</v>
+        <v>311</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46196</v>
+        <v>46216</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1685410</v>
+        <v>648900</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>677750</v>
+        <v>569379</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>128</v>
+        <v>312</v>
       </c>
       <c r="I61" s="5" t="n">
         <f aca="false">IF(OR(F61="",G61=""),"",(F61-G61)/G61)</f>
-        <v>1.48677240870527</v>
+        <v>0.139662685135911</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K61" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>314</v>
+      </c>
       <c r="L61" s="2" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R61" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>281</v>
+        <v>22</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>46065</v>
+        <v>46204</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>204406</v>
+        <v>1516971</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>160078.5</v>
+        <v>886828.54</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="I62" s="5" t="n">
         <f aca="false">IF(OR(F62="",G62=""),"",(F62-G62)/G62)</f>
-        <v>0.276911015533004</v>
+        <v>0.710557262850381</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>287</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="M62" s="2"/>
       <c r="N62" s="2"/>
       <c r="O62" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R62" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>290</v>
+        <v>126</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>283</v>
+        <v>323</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>284</v>
+        <v>43</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>46065</v>
+        <v>46196</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>275750</v>
+        <v>1685410</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>160078.5</v>
+        <v>677750</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>285</v>
+        <v>139</v>
       </c>
       <c r="I63" s="5" t="n">
         <f aca="false">IF(OR(F63="",G63=""),"",(F63-G63)/G63)</f>
-        <v>0.722592353126747</v>
+        <v>1.48677240870527</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>292</v>
+        <v>325</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R63" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>295</v>
+        <v>328</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>298</v>
+        <v>331</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46056</v>
+        <v>46065</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>47500</v>
+        <v>204406</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>37000</v>
+        <v>160078.5</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>299</v>
+        <v>332</v>
       </c>
       <c r="I64" s="5" t="n">
         <f aca="false">IF(OR(F64="",G64=""),"",(F64-G64)/G64)</f>
-        <v>0.283783783783784</v>
+        <v>0.276911015533004</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R64" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>125</v>
+        <v>337</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>42</v>
+        <v>331</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>46252</v>
+        <v>46065</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>7511988</v>
+        <v>275750</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>3673989.12</v>
+        <v>160078.5</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="I65" s="5" t="n">
         <f aca="false">IF(OR(F65="",G65=""),"",(F65-G65)/G65)</f>
-        <v>1.04464078543597</v>
+        <v>0.722592353126747</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
+      <c r="L65" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="O65" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R65" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>92</v>
+        <v>344</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>46246</v>
+        <v>46056</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>216657</v>
+        <v>47500</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>125000</v>
+        <v>37000</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>93</v>
+        <v>346</v>
       </c>
       <c r="I66" s="5" t="n">
         <f aca="false">IF(OR(F66="",G66=""),"",(F66-G66)/G66)</f>
-        <v>0.733256</v>
+        <v>0.283783783783784</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K66" s="2"/>
       <c r="L66" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2" t="s">
-        <v>310</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R66" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>313</v>
+        <v>112</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>92</v>
+        <v>350</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>267400</v>
+        <v>7511988</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>125000</v>
+        <v>3673989.12</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>93</v>
+        <v>351</v>
       </c>
       <c r="I67" s="5" t="n">
         <f aca="false">IF(OR(F67="",G67=""),"",(F67-G67)/G67)</f>
-        <v>1.1392</v>
+        <v>1.04464078543597</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R67" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>21</v>
@@ -5552,47 +5735,55 @@
         <v>46246</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>274975</v>
+        <v>216657</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>125000</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I68" s="5" t="n">
         <f aca="false">IF(OR(F68="",G68=""),"",(F68-G68)/G68)</f>
-        <v>1.1998</v>
+        <v>0.733256</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>358</v>
+      </c>
       <c r="O68" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R68" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>21</v>
@@ -5601,47 +5792,47 @@
         <v>46246</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>311500</v>
+        <v>274975</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>125000</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I69" s="5" t="n">
         <f aca="false">IF(OR(F69="",G69=""),"",(F69-G69)/G69)</f>
-        <v>1.492</v>
+        <v>1.1998</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R69" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>21</v>
@@ -5650,47 +5841,47 @@
         <v>46246</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>336037</v>
+        <v>311500</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>125000</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I70" s="5" t="n">
         <f aca="false">IF(OR(F70="",G70=""),"",(F70-G70)/G70)</f>
-        <v>1.688296</v>
+        <v>1.492</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R70" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>323</v>
+        <v>366</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>21</v>
@@ -5699,148 +5890,148 @@
         <v>46246</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>528000</v>
+        <v>336037</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>125000</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I71" s="5" t="n">
         <f aca="false">IF(OR(F71="",G71=""),"",(F71-G71)/G71)</f>
-        <v>3.224</v>
+        <v>1.688296</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R71" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>324</v>
+        <v>368</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>125</v>
+        <v>369</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2194289.14</v>
+        <v>528000</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1694675</v>
+        <v>125000</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="I72" s="5" t="n">
         <f aca="false">IF(OR(F72="",G72=""),"",(F72-G72)/G72)</f>
-        <v>0.294814132503282</v>
+        <v>3.224</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R72" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>326</v>
+        <v>112</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>327</v>
+        <v>148</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>328</v>
+        <v>43</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>247000</v>
+        <v>2194289.14</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>177500</v>
+        <v>1694675</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>329</v>
+        <v>44</v>
       </c>
       <c r="I73" s="5" t="n">
         <f aca="false">IF(OR(F73="",G73=""),"",(F73-G73)/G73)</f>
-        <v>0.391549295774648</v>
+        <v>0.294814132503282</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R73" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>46232</v>
@@ -5852,44 +6043,44 @@
         <v>177500</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="I74" s="5" t="n">
         <f aca="false">IF(OR(F74="",G74=""),"",(F74-G74)/G74)</f>
         <v>0.870422535211268</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>331</v>
+        <v>372</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R74" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>46224</v>
@@ -5901,44 +6092,44 @@
         <v>890013.65</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I75" s="5" t="n">
         <f aca="false">IF(OR(F75="",G75=""),"",(F75-G75)/G75)</f>
         <v>0.16233048785263</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>333</v>
+        <v>374</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R75" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>46216</v>
@@ -5950,44 +6141,44 @@
         <v>569379</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>268</v>
+        <v>312</v>
       </c>
       <c r="I76" s="5" t="n">
         <f aca="false">IF(OR(F76="",G76=""),"",(F76-G76)/G76)</f>
         <v>0.535234000551478</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R76" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="E77" s="3" t="n">
         <v>46216</v>
@@ -5999,44 +6190,44 @@
         <v>569379</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>268</v>
+        <v>312</v>
       </c>
       <c r="I77" s="5" t="n">
         <f aca="false">IF(OR(F77="",G77=""),"",(F77-G77)/G77)</f>
         <v>0.592085412352756</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R77" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E78" s="3" t="n">
         <v>46196</v>
@@ -6048,44 +6239,44 @@
         <v>677750</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="I78" s="5" t="n">
         <f aca="false">IF(OR(F78="",G78=""),"",(F78-G78)/G78)</f>
         <v>1.03802369605312</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R78" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="E79" s="3" t="n">
         <v>46185</v>
@@ -6097,44 +6288,44 @@
         <v>33400</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="I79" s="5" t="n">
         <f aca="false">IF(OR(F79="",G79=""),"",(F79-G79)/G79)</f>
         <v>0.425149700598802</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R79" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>46156</v>
@@ -6146,44 +6337,44 @@
         <v>196400</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="I80" s="5" t="n">
         <f aca="false">IF(OR(F80="",G80=""),"",(F80-G80)/G80)</f>
         <v>0.680244399185336</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R80" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>46156</v>
@@ -6195,44 +6386,44 @@
         <v>196400</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="I81" s="5" t="n">
         <f aca="false">IF(OR(F81="",G81=""),"",(F81-G81)/G81)</f>
         <v>0.844704684317719</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R81" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>46156</v>
@@ -6244,44 +6435,44 @@
         <v>196400</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="I82" s="5" t="n">
         <f aca="false">IF(OR(F82="",G82=""),"",(F82-G82)/G82)</f>
         <v>1.14154786150713</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R82" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>347</v>
+        <v>388</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="E83" s="3" t="n">
         <v>46156</v>
@@ -6293,44 +6484,44 @@
         <v>196400</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="I83" s="5" t="n">
         <f aca="false">IF(OR(F83="",G83=""),"",(F83-G83)/G83)</f>
         <v>1.37270875763747</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R83" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="E84" s="3" t="n">
         <v>46156</v>
@@ -6342,44 +6533,44 @@
         <v>196400</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="I84" s="5" t="n">
         <f aca="false">IF(OR(F84="",G84=""),"",(F84-G84)/G84)</f>
         <v>1.89601323828921</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R84" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>349</v>
+        <v>390</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="E85" s="3" t="n">
         <v>46065</v>
@@ -6391,44 +6582,44 @@
         <v>160078.5</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="I85" s="5" t="n">
         <f aca="false">IF(OR(F85="",G85=""),"",(F85-G85)/G85)</f>
         <v>0.787747886193336</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R85" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>351</v>
+        <v>392</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="E86" s="3" t="n">
         <v>46056</v>
@@ -6440,44 +6631,44 @@
         <v>37000</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="I86" s="5" t="n">
         <f aca="false">IF(OR(F86="",G86=""),"",(F86-G86)/G86)</f>
         <v>0.866113513513513</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R86" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="E87" s="3" t="n">
         <v>46056</v>
@@ -6489,44 +6680,44 @@
         <v>37000</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="I87" s="5" t="n">
         <f aca="false">IF(OR(F87="",G87=""),"",(F87-G87)/G87)</f>
         <v>0.101567567567568</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R87" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>355</v>
+        <v>396</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="E88" s="3" t="n">
         <v>46056</v>
@@ -6538,44 +6729,44 @@
         <v>37000</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="I88" s="5" t="n">
         <f aca="false">IF(OR(F88="",G88=""),"",(F88-G88)/G88)</f>
         <v>0.35</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R88" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="E89" s="3" t="n">
         <v>46056</v>
@@ -6587,41 +6778,41 @@
         <v>37000</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="I89" s="5" t="n">
         <f aca="false">IF(OR(F89="",G89=""),"",(F89-G89)/G89)</f>
         <v>0.835513513513514</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R89" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>358</v>
+        <v>399</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>21</v>
@@ -6636,35 +6827,35 @@
         <v>125000</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I90" s="5" t="n">
         <f aca="false">IF(OR(F90="",G90=""),"",(F90-G90)/G90)</f>
         <v>0.876</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>360</v>
+        <v>401</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R90" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -6792,28 +6983,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>362</v>
+        <v>403</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>363</v>
+        <v>404</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>364</v>
+        <v>405</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>16</v>
@@ -6821,872 +7012,872 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>372</v>
+        <v>413</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>378</v>
+        <v>419</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>387</v>
+        <v>428</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>389</v>
+        <v>430</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>390</v>
+        <v>431</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>391</v>
+        <v>432</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>392</v>
+        <v>433</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>401</v>
+        <v>442</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>404</v>
+        <v>445</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>406</v>
+        <v>447</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>408</v>
+        <v>449</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>412</v>
+        <v>453</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>415</v>
+        <v>456</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="G9" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>377</v>
-      </c>
       <c r="I9" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>423</v>
+        <v>464</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>424</v>
+        <v>465</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>425</v>
+        <v>466</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>427</v>
+        <v>468</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>429</v>
+        <v>470</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>435</v>
+        <v>476</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>441</v>
+        <v>482</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>445</v>
+        <v>486</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>450</v>
+        <v>491</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>455</v>
+        <v>496</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>457</v>
+        <v>498</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>461</v>
+        <v>502</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>462</v>
+        <v>503</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>463</v>
+        <v>504</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>465</v>
+        <v>506</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>469</v>
+        <v>510</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>477</v>
+        <v>518</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>478</v>
+        <v>519</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>481</v>
+        <v>522</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>482</v>
+        <v>523</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>483</v>
+        <v>524</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>484</v>
+        <v>525</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>485</v>
+        <v>526</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>488</v>
+        <v>529</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>490</v>
+        <v>531</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>493</v>
+        <v>534</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>500</v>
+        <v>541</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>507</v>
+        <v>548</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>510</v>
+        <v>551</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>512</v>
+        <v>553</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>514</v>
+        <v>555</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>520</v>
+        <v>561</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>523</v>
+        <v>564</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>525</v>
+        <v>566</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>526</v>
+        <v>567</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>527</v>
+        <v>568</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -7745,32 +7936,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>528</v>
+        <v>569</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>529</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>530</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>531</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>532</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>533</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
